--- a/workbook/Wolf Cola_Manufacturing_Line_Productivity.xlsx
+++ b/workbook/Wolf Cola_Manufacturing_Line_Productivity.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1dd041bb3dd47639/Documents/GitHub/Wolf-Cola-Manufacturing-Downtime/workbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{DEBB2F9C-A5BA-4D6B-9F10-E30212C246C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A888163-8AB1-4FB5-98EC-C858585A9DEB}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{DEBB2F9C-A5BA-4D6B-9F10-E30212C246C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D975E92D-4841-4367-868D-259EDF6E488D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1137,6 +1137,7 @@
     <xf numFmtId="0" fontId="28" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1177,42 +1178,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="10">
-    <dxf>
-      <font>
-        <color theme="1" tint="0.249977111117893"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF2EEE6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF916140"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF401801"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <color theme="0"/>
@@ -1250,6 +1220,36 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFD5BCAA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1" tint="0.249977111117893"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF2EEE6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF916140"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF401801"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1314,6 +1314,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF401801"/>
+      <color rgb="FFF3EFE7"/>
       <color rgb="FF4A2108"/>
       <color rgb="FFB77A55"/>
       <color rgb="FFD2C7B9"/>
@@ -1321,9 +1323,7 @@
       <color rgb="FF766E65"/>
       <color rgb="FF8F4218"/>
       <color rgb="FFF0EBE3"/>
-      <color rgb="FFF3EFE7"/>
       <color rgb="FFD5BCAA"/>
-      <color rgb="FFE4D8CB"/>
     </mruColors>
   </colors>
   <extLst>
@@ -9381,6 +9381,93 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F867B5F7-6867-41B2-B9F0-6B1CC0BC3B71}" name="PivotTable6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:D8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="13">
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="14" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0">
+      <items count="7">
+        <item x="5"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" numFmtId="165" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="165" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" numFmtId="1" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="1" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="1" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="10" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="10" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="Count of Batch" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Actual Batch Time" fld="7" baseField="0" baseItem="0" numFmtId="1"/>
+    <dataField name="Sum of Recorded Downtime Minutes" fld="9" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C9629DFA-CCB6-4FE8-857B-DFE91936D882}" name="PivotTable7" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A13:M19" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="7">
@@ -9480,7 +9567,7 @@
     <dataField name="Sum of Downtime Minutes" fld="2" baseField="0" baseItem="0" numFmtId="1"/>
   </dataFields>
   <conditionalFormats count="3">
-    <conditionalFormat priority="1">
+    <conditionalFormat priority="3">
       <pivotAreas count="1">
         <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="3">
@@ -9540,7 +9627,7 @@
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="3">
+    <conditionalFormat priority="1">
       <pivotAreas count="1">
         <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="3">
@@ -9571,93 +9658,6 @@
       </pivotAreas>
     </conditionalFormat>
   </conditionalFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F867B5F7-6867-41B2-B9F0-6B1CC0BC3B71}" name="PivotTable6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
-  <location ref="A3:D8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="13">
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="14" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0">
-      <items count="7">
-        <item x="5"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="5">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" numFmtId="165" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="165" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" numFmtId="1" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="1" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="1" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="10" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="10" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-  </colItems>
-  <dataFields count="3">
-    <dataField name="Count of Batch" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Sum of Actual Batch Time" fld="7" baseField="0" baseItem="0" numFmtId="1"/>
-    <dataField name="Sum of Recorded Downtime Minutes" fld="9" baseField="0" baseItem="0"/>
-  </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -10104,27 +10104,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A1" s="94"/>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-      <c r="M1" s="94"/>
-      <c r="N1" s="94"/>
-      <c r="O1" s="94"/>
-      <c r="P1" s="94"/>
-      <c r="Q1" s="94"/>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
-      <c r="U1" s="94"/>
+      <c r="A1" s="80"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="80"/>
+      <c r="O1" s="80"/>
+      <c r="P1" s="80"/>
+      <c r="Q1" s="80"/>
+      <c r="R1" s="80"/>
+      <c r="S1" s="80"/>
+      <c r="T1" s="80"/>
+      <c r="U1" s="80"/>
     </row>
     <row r="2" spans="1:23" s="29" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="1">
       <c r="A2" s="54" t="s">
@@ -10170,13 +10170,13 @@
       <c r="N3" s="28"/>
       <c r="O3" s="28"/>
       <c r="P3" s="28"/>
-      <c r="Q3" s="83" t="s">
+      <c r="Q3" s="84" t="s">
         <v>147</v>
       </c>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
+      <c r="R3" s="84"/>
+      <c r="S3" s="84"/>
+      <c r="T3" s="84"/>
+      <c r="U3" s="84"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" s="31"/>
@@ -10205,29 +10205,29 @@
       <c r="A5" s="33"/>
       <c r="B5" s="33"/>
       <c r="C5" s="33"/>
-      <c r="D5" s="89" t="s">
+      <c r="D5" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
       <c r="G5" s="34"/>
-      <c r="H5" s="90" t="s">
+      <c r="H5" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="I5" s="90"/>
-      <c r="J5" s="90"/>
+      <c r="I5" s="91"/>
+      <c r="J5" s="91"/>
       <c r="K5" s="34"/>
-      <c r="L5" s="90" t="s">
+      <c r="L5" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="M5" s="90"/>
-      <c r="N5" s="90"/>
+      <c r="M5" s="91"/>
+      <c r="N5" s="91"/>
       <c r="O5" s="34"/>
-      <c r="P5" s="90" t="s">
+      <c r="P5" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="Q5" s="90"/>
-      <c r="R5" s="90"/>
+      <c r="Q5" s="91"/>
+      <c r="R5" s="91"/>
       <c r="S5" s="32"/>
       <c r="T5" s="32"/>
       <c r="U5" s="32"/>
@@ -10238,33 +10238,33 @@
       <c r="A6" s="35"/>
       <c r="B6" s="35"/>
       <c r="C6" s="35"/>
-      <c r="D6" s="81">
+      <c r="D6" s="82">
         <f>'EDA Summary'!B1</f>
         <v>0.64022809745982379</v>
       </c>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
       <c r="G6" s="36"/>
-      <c r="H6" s="91">
+      <c r="H6" s="92">
         <f>'EDA Summary'!B8</f>
         <v>0.35977190254017632</v>
       </c>
-      <c r="I6" s="91"/>
-      <c r="J6" s="91"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="92"/>
       <c r="K6" s="36"/>
-      <c r="L6" s="80" t="str">
+      <c r="L6" s="81" t="str">
         <f>INT('EDA Summary'!B5/60)&amp;"h "&amp;MOD('EDA Summary'!B5,60)&amp;"m"</f>
         <v>23h 8m</v>
       </c>
-      <c r="M6" s="80"/>
-      <c r="N6" s="80"/>
+      <c r="M6" s="81"/>
+      <c r="N6" s="81"/>
       <c r="O6" s="37"/>
-      <c r="P6" s="80">
+      <c r="P6" s="81">
         <f>COUNTA('Fact Downtime'!A2:A62)</f>
         <v>61</v>
       </c>
-      <c r="Q6" s="80"/>
-      <c r="R6" s="80"/>
+      <c r="Q6" s="81"/>
+      <c r="R6" s="81"/>
       <c r="S6" s="38"/>
       <c r="T6" s="38"/>
       <c r="U6" s="38"/>
@@ -10275,29 +10275,29 @@
       <c r="A7" s="33"/>
       <c r="B7" s="33"/>
       <c r="C7" s="33"/>
-      <c r="D7" s="87" t="s">
+      <c r="D7" s="88" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="87"/>
-      <c r="F7" s="87"/>
+      <c r="E7" s="88"/>
+      <c r="F7" s="88"/>
       <c r="G7" s="39"/>
-      <c r="H7" s="88" t="s">
+      <c r="H7" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="88"/>
-      <c r="J7" s="88"/>
+      <c r="I7" s="89"/>
+      <c r="J7" s="89"/>
       <c r="K7" s="39"/>
-      <c r="L7" s="88" t="s">
+      <c r="L7" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="88"/>
-      <c r="N7" s="88"/>
+      <c r="M7" s="89"/>
+      <c r="N7" s="89"/>
       <c r="O7" s="39"/>
-      <c r="P7" s="88" t="s">
+      <c r="P7" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="Q7" s="88"/>
-      <c r="R7" s="88"/>
+      <c r="Q7" s="89"/>
+      <c r="R7" s="89"/>
       <c r="S7" s="32"/>
       <c r="T7" s="32"/>
       <c r="U7" s="32"/>
@@ -10835,20 +10835,20 @@
       <c r="E30" s="44"/>
       <c r="F30" s="44"/>
       <c r="G30" s="45"/>
-      <c r="H30" s="84" t="s">
+      <c r="H30" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="I30" s="85"/>
-      <c r="J30" s="85"/>
-      <c r="K30" s="85"/>
-      <c r="L30" s="85"/>
-      <c r="M30" s="85"/>
-      <c r="N30" s="85"/>
-      <c r="O30" s="85"/>
-      <c r="P30" s="85"/>
-      <c r="Q30" s="85"/>
-      <c r="R30" s="85"/>
-      <c r="S30" s="86"/>
+      <c r="I30" s="86"/>
+      <c r="J30" s="86"/>
+      <c r="K30" s="86"/>
+      <c r="L30" s="86"/>
+      <c r="M30" s="86"/>
+      <c r="N30" s="86"/>
+      <c r="O30" s="86"/>
+      <c r="P30" s="86"/>
+      <c r="Q30" s="86"/>
+      <c r="R30" s="86"/>
+      <c r="S30" s="87"/>
       <c r="T30" s="45"/>
       <c r="U30" s="33"/>
     </row>
@@ -10877,7 +10877,7 @@
       <c r="V31" s="7"/>
       <c r="W31" s="7"/>
     </row>
-    <row r="32" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:26" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A32" s="33"/>
       <c r="B32" s="44"/>
       <c r="C32" s="44"/>
@@ -11124,12 +11124,12 @@
       <c r="J38" s="53"/>
       <c r="K38" s="53"/>
       <c r="L38" s="53"/>
-      <c r="M38" s="82" t="s">
+      <c r="M38" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="N38" s="82"/>
-      <c r="O38" s="82"/>
-      <c r="P38" s="82"/>
+      <c r="N38" s="83"/>
+      <c r="O38" s="83"/>
+      <c r="P38" s="83"/>
       <c r="Q38" s="53"/>
       <c r="R38" s="53"/>
       <c r="S38" s="62"/>
@@ -11945,18 +11945,18 @@
     <mergeCell ref="L6:N6"/>
   </mergeCells>
   <conditionalFormatting sqref="I33:S36">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="between">
       <formula>25</formula>
       <formula>49</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="11" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="11" operator="lessThan">
       <formula>25</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="12" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="12" operator="between">
       <formula>50</formula>
       <formula>99</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="13" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="0" priority="13" operator="greaterThanOrEqual">
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12691,18 +12691,18 @@
     </row>
   </sheetData>
   <conditionalFormatting pivot="1" sqref="B15:L18">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="greaterThanOrEqual">
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="B15:L18">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="between">
       <formula>50</formula>
       <formula>99</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="B15:L18">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="between">
       <formula>1</formula>
       <formula>49</formula>
     </cfRule>
@@ -17589,20 +17589,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B1" s="92" t="s">
+      <c r="B1" s="93" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="93"/>
-      <c r="J1" s="93"/>
-      <c r="K1" s="93"/>
-      <c r="L1" s="93"/>
-      <c r="M1" s="93"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="94"/>
     </row>
     <row r="2" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
